--- a/artfynd/A 25698-2026 artfynd.xlsx
+++ b/artfynd/A 25698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134433344</v>
+        <v>134433334</v>
       </c>
       <c r="B2" t="n">
-        <v>81348</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>390213</v>
+        <v>390309</v>
       </c>
       <c r="R2" t="n">
-        <v>6760320</v>
+        <v>6760404</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134433341</v>
+        <v>134433344</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>81355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390155</v>
+        <v>390213</v>
       </c>
       <c r="R3" t="n">
-        <v>6760343</v>
+        <v>6760320</v>
       </c>
       <c r="S3" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134433340</v>
+        <v>134433325</v>
       </c>
       <c r="B4" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>390145</v>
+        <v>390488</v>
       </c>
       <c r="R4" t="n">
-        <v>6760367</v>
+        <v>6760411</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134433343</v>
+        <v>134433326</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390195</v>
+        <v>390467</v>
       </c>
       <c r="R5" t="n">
-        <v>6760321</v>
+        <v>6760411</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134433336</v>
+        <v>134433327</v>
       </c>
       <c r="B6" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>390267</v>
+        <v>390455</v>
       </c>
       <c r="R6" t="n">
-        <v>6760399</v>
+        <v>6760391</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134433342</v>
+        <v>134433329</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>390184</v>
+        <v>390420</v>
       </c>
       <c r="R7" t="n">
-        <v>6760324</v>
+        <v>6760374</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134433337</v>
+        <v>134433330</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>390262</v>
+        <v>390394</v>
       </c>
       <c r="R8" t="n">
-        <v>6760401</v>
+        <v>6760389</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134433347</v>
+        <v>134433331</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>390268</v>
+        <v>390361</v>
       </c>
       <c r="R9" t="n">
-        <v>6760346</v>
+        <v>6760380</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134433338</v>
+        <v>134433332</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>390252</v>
+        <v>390338</v>
       </c>
       <c r="R10" t="n">
-        <v>6760402</v>
+        <v>6760377</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134433339</v>
+        <v>134433333</v>
       </c>
       <c r="B11" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>390200</v>
+        <v>390331</v>
       </c>
       <c r="R11" t="n">
-        <v>6760392</v>
+        <v>6760389</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134433351</v>
+        <v>134433335</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>390371</v>
+        <v>390277</v>
       </c>
       <c r="R12" t="n">
-        <v>6760340</v>
+        <v>6760389</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134433334</v>
+        <v>134433337</v>
       </c>
       <c r="B13" t="n">
-        <v>79398</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>390309</v>
+        <v>390262</v>
       </c>
       <c r="R13" t="n">
-        <v>6760404</v>
+        <v>6760401</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134433333</v>
+        <v>134433338</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>390331</v>
+        <v>390252</v>
       </c>
       <c r="R14" t="n">
-        <v>6760389</v>
+        <v>6760402</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134433327</v>
+        <v>134433341</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>390455</v>
+        <v>390155</v>
       </c>
       <c r="R15" t="n">
-        <v>6760391</v>
+        <v>6760343</v>
       </c>
       <c r="S15" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134433349</v>
+        <v>134433342</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>390282</v>
+        <v>390184</v>
       </c>
       <c r="R16" t="n">
-        <v>6760357</v>
+        <v>6760324</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,14 +2280,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134433352</v>
+        <v>134433347</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>390408</v>
+        <v>390268</v>
       </c>
       <c r="R17" t="n">
-        <v>6760334</v>
+        <v>6760346</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,14 +2387,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134433329</v>
+        <v>134433349</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>390420</v>
+        <v>390282</v>
       </c>
       <c r="R18" t="n">
-        <v>6760374</v>
+        <v>6760357</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134433353</v>
+        <v>134433351</v>
       </c>
       <c r="B19" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>390425</v>
+        <v>390371</v>
       </c>
       <c r="R19" t="n">
-        <v>6760356</v>
+        <v>6760340</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,14 +2601,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134433330</v>
+        <v>134433352</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>390394</v>
+        <v>390408</v>
       </c>
       <c r="R20" t="n">
-        <v>6760389</v>
+        <v>6760334</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134433355</v>
+        <v>134433354</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>390487</v>
+        <v>390477</v>
       </c>
       <c r="R21" t="n">
-        <v>6760400</v>
+        <v>6760376</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,14 +2815,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134433325</v>
+        <v>134433355</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>390488</v>
+        <v>390487</v>
       </c>
       <c r="R22" t="n">
-        <v>6760411</v>
+        <v>6760400</v>
       </c>
       <c r="S22" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134433335</v>
+        <v>134433328</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>390277</v>
+        <v>390438</v>
       </c>
       <c r="R23" t="n">
-        <v>6760389</v>
+        <v>6760385</v>
       </c>
       <c r="S23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134433328</v>
+        <v>134433336</v>
       </c>
       <c r="B24" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>390438</v>
+        <v>390267</v>
       </c>
       <c r="R24" t="n">
-        <v>6760385</v>
+        <v>6760399</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134433350</v>
+        <v>134433339</v>
       </c>
       <c r="B25" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>390328</v>
+        <v>390200</v>
       </c>
       <c r="R25" t="n">
-        <v>6760350</v>
+        <v>6760392</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134433354</v>
+        <v>134433340</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>390477</v>
+        <v>390145</v>
       </c>
       <c r="R26" t="n">
-        <v>6760376</v>
+        <v>6760367</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134433326</v>
+        <v>134433345</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390467</v>
+        <v>390213</v>
       </c>
       <c r="R27" t="n">
-        <v>6760411</v>
+        <v>6760318</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134433332</v>
+        <v>134433350</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390338</v>
+        <v>390328</v>
       </c>
       <c r="R28" t="n">
-        <v>6760377</v>
+        <v>6760350</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134433331</v>
+        <v>134433353</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390361</v>
+        <v>390425</v>
       </c>
       <c r="R29" t="n">
-        <v>6760380</v>
+        <v>6760356</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,6 +3668,220 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134433343</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>390195</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6760321</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134433346</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>390213</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6760318</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25698-2026 artfynd.xlsx
+++ b/artfynd/A 25698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433344</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433327</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433329</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433330</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433331</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433332</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433333</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433335</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433337</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433338</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433341</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433342</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433347</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433349</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433351</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433352</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433354</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433355</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433328</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433336</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433339</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433340</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433345</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433350</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433353</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433343</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,8 +4032,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>